--- a/data/trans_orig/IP1001-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1001-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132744</t>
+          <t>132412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138021</t>
+          <t>138018</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148259</t>
+          <t>148833</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284529</t>
+          <t>284048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290407</t>
+          <t>290382</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185980</t>
+          <t>186379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192772</t>
+          <t>192829</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201439</t>
+          <t>202076</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209409</t>
+          <t>209480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390624</t>
+          <t>389983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>401091</t>
+          <t>400813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10971</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>15041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>126846</t>
+          <t>127327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134525</t>
+          <t>134369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142781</t>
+          <t>143372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148537</t>
+          <t>148534</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>273003</t>
+          <t>272433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281953</t>
+          <t>281930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>15653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23707</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197125</t>
+          <t>196339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206028</t>
+          <t>205722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193258</t>
+          <t>192171</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>203166</t>
+          <t>202736</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393432</t>
+          <t>393180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>406776</t>
+          <t>407467</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28151</t>
+          <t>28995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>27270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30612</t>
+          <t>30674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50416</t>
+          <t>50444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>652870</t>
+          <t>652026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>667138</t>
+          <t>666395</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>695492</t>
+          <t>695430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>709467</t>
+          <t>709648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1353305</t>
+          <t>1353277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1373109</t>
+          <t>1373047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10527</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14738</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125864</t>
+          <t>125484</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134036</t>
+          <t>134120</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146865</t>
+          <t>146558</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152455</t>
+          <t>152418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>274751</t>
+          <t>275614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>285091</t>
+          <t>285532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>198470</t>
+          <t>198188</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204192</t>
+          <t>204122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211060</t>
+          <t>210443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>219390</t>
+          <t>219423</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>412788</t>
+          <t>412374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>422747</t>
+          <t>422872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>438</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150359</t>
+          <t>149990</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154396</t>
+          <t>154401</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160346</t>
+          <t>160356</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165365</t>
+          <t>165361</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>312913</t>
+          <t>312472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319504</t>
+          <t>319134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14818</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>201939</t>
+          <t>203126</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>209550</t>
+          <t>209555</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192264</t>
+          <t>192257</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202788</t>
+          <t>202727</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398401</t>
+          <t>399103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>410756</t>
+          <t>411021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20761</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28950</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>24619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44239</t>
+          <t>44180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>686167</t>
+          <t>686636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>698439</t>
+          <t>699072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>719808</t>
+          <t>719904</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>734724</t>
+          <t>735327</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1411447</t>
+          <t>1411506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1430881</t>
+          <t>1431067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>863</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>735</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126056</t>
+          <t>125534</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132879</t>
+          <t>132844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140900</t>
+          <t>141368</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147333</t>
+          <t>147341</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>269866</t>
+          <t>270625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>279014</t>
+          <t>278968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11971</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21923</t>
+          <t>22012</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>193563</t>
+          <t>193732</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202658</t>
+          <t>202747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>212388</t>
+          <t>212503</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>220615</t>
+          <t>220683</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>409683</t>
+          <t>409594</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>421504</t>
+          <t>421615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151561</t>
+          <t>151781</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158997</t>
+          <t>159575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165468</t>
+          <t>165350</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313340</t>
+          <t>313804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320654</t>
+          <t>320709</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>200194</t>
+          <t>200013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206638</t>
+          <t>206645</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194495</t>
+          <t>194191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202877</t>
+          <t>202814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>397992</t>
+          <t>398206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>408481</t>
+          <t>408409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>23805</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>27885</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>25800</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46007</t>
+          <t>44912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>680332</t>
+          <t>680566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>693939</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>718119</t>
+          <t>716959</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>732128</t>
+          <t>731517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1403208</t>
+          <t>1404303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1423061</t>
+          <t>1423415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>721</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>111559</t>
+          <t>110203</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116558</t>
+          <t>116559</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>134884</t>
+          <t>134672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139857</t>
+          <t>139885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248911</t>
+          <t>248247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255823</t>
+          <t>255923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>19156</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>24302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>180039</t>
+          <t>180546</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188666</t>
+          <t>188942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235555</t>
+          <t>235879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>248291</t>
+          <t>248807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>421301</t>
+          <t>421246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>435441</t>
+          <t>435999</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20763</t>
+          <t>20882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>28266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>180730</t>
+          <t>180410</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>188278</t>
+          <t>188150</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164523</t>
+          <t>164404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182298</t>
+          <t>182503</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>348969</t>
+          <t>346605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>368893</t>
+          <t>368695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161352</t>
+          <t>161149</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167183</t>
+          <t>167199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171353</t>
+          <t>171397</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179460</t>
+          <t>179391</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>335650</t>
+          <t>335079</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>345211</t>
+          <t>345567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>30855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56621</t>
+          <t>58133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>643379</t>
+          <t>643907</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>656632</t>
+          <t>656616</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>721801</t>
+          <t>720777</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744728</t>
+          <t>743244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1370691</t>
+          <t>1369179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1396983</t>
+          <t>1396457</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1001-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1001-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4196</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2226</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6314</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6675</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4244</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>151697</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>148881</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>136500</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>132412</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>138018</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>132051</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>138019</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,4%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,49%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>151697</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>148833</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>424</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284048</t>
+          <t>283103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290382</t>
+          <t>290421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5944</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2627</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11275</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4938</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2334</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8784</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9396</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5944</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2662</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10066</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17322</t>
+          <t>16838</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>206198</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>200867</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>209515</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>190225</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>186379</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>192829</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>185767</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>192808</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>206198</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>202076</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>209480</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>389983</t>
+          <t>390467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>400813</t>
+          <t>400769</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6743</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6348</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3448</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10490</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3392</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10866</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,61%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>146753</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>142914</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148534</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>131469</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>127327</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>134369</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>126951</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>134425</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,39%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>146753</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>143372</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>148534</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,06%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>272433</t>
+          <t>271998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281930</t>
+          <t>282184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9048</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5221</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14853</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7024</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3593</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12976</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3652</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12227</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,36%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9048</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5088</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15653</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23959</t>
+          <t>24241</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>198776</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>192971</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>202291</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>196339</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>205722</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>197088</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>205663</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,64%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>198776</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>192171</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202736</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,65%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393180</t>
+          <t>392898</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>407467</t>
+          <t>406329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19277</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13421</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27329</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>20535</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14626</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>28995</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14301</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>29054</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>19277</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13052</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>27270</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30674</t>
+          <t>30919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50444</t>
+          <t>50899</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1057</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>703423</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>695371</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>709279</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>987</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>660486</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>652026</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>666395</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>651967</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>666720</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,74%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1057</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>703423</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>695430</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>709648</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1353277</t>
+          <t>1352822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1373047</t>
+          <t>1372802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2692</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6417</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5538</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2271</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10907</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10672</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,06%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2692</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6540</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>150406</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>146681</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>152412</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>130853</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>125484</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>134120</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>125719</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>134046</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,94%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>150406</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>146558</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>152418</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275614</t>
+          <t>274860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>285532</t>
+          <t>284917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3169</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11683</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3187</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7210</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1217</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6966</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3170</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12150</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>14891</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>216178</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>210910</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>219424</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>202211</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>198188</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>204122</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>198432</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>204181</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>216178</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>210443</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>219423</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>412374</t>
+          <t>413100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>422872</t>
+          <t>422733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>222593</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>222593</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>222593</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>222593</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>222593</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>222593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,74 +3356,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2447</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5596</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1755</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4849</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4847</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>3,13%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2447</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5629</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>163538</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>160389</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165363</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>153084</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149990</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154401</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>149992</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>154398</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,87%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>96,87%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,72%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>163538</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>160356</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165361</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>489</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>312472</t>
+          <t>311967</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319134</t>
+          <t>318969</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8460</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4878</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14344</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2968</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7174</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7111</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8460</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4355</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14825</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>198622</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>192738</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202204</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>207332</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>203126</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>209555</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>203189</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>209389</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,59%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>198622</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>192257</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202727</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,91%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399103</t>
+          <t>398333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>411021</t>
+          <t>410704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>28897</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>13448</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7856</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20292</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8232</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20330</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20013</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13431</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>28854</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24619</t>
+          <t>24595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44180</t>
+          <t>44948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>728745</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>719861</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>735171</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,14%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>999</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>693480</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>686636</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>699072</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>686598</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>698696</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,1%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>728745</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>719904</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>735327</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1411506</t>
+          <t>1410738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1431067</t>
+          <t>1431091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748758</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748758</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748758</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748758</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748758</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748758</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4622,67 +4622,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2960</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7312</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>3111</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8173</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8143</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2960</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6708</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11158</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>145116</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>140764</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,06%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>130596</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>125534</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>132844</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>125564</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>132869</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,67%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>145116</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>141368</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>147341</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>270625</t>
+          <t>270468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>278968</t>
+          <t>278896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6943</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3694</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11751</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8329</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13515</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4363</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13699</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6943</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3676</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11856</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22012</t>
+          <t>23217</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -5078,67 +5078,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>217416</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>212608</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>220665</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>198918</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>193732</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>202747</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>193548</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>202884</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,98%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>217416</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>212503</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>220683</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>409594</t>
+          <t>408389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>421615</t>
+          <t>421119</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7185</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1321</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4216</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4071</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7098</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>163303</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>159488</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165415</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,69%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154676</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151781</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>151926</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,15%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>163303</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>159575</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165350</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,98%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,74%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>500</t>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313804</t>
+          <t>313333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320709</t>
+          <t>320659</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5981</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11183</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3001</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7407</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5981</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2922</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11545</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>199755</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>194553</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202947</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>204419</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>200013</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>206645</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>200299</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>206655</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,55%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,57%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>199755</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>194191</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202814</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,39%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>559</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398206</t>
+          <t>397843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>408409</t>
+          <t>408100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13025</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27863</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>15761</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10516</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>23805</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10036</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>23232</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>19253</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13327</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>27885</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25800</t>
+          <t>26405</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44912</t>
+          <t>46378</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>725591</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>716981</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>731819</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1038</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>688610</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>680566</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>693855</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>681139</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>694335</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,76%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1037</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>725591</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>716959</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>731517</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1404303</t>
+          <t>1402837</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1423415</t>
+          <t>1422810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2268</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5551</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2310</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>721</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7077</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>759</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>123638</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>120355</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>125350</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>114970</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>110203</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>116559</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>138122</t>
+          <t>118650</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>134672</t>
+          <t>114771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139885</t>
+          <t>120312</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>253093</t>
+          <t>242287</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248247</t>
+          <t>238168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255923</t>
+          <t>245014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10740</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6533</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18351</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4585</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1570</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9966</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24302</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>226466</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>218855</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>230673</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>185927</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>180546</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>188942</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,77%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>243498</t>
+          <t>179600</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235879</t>
+          <t>174648</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>248807</t>
+          <t>182514</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>429426</t>
+          <t>406066</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>421246</t>
+          <t>396625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>435999</t>
+          <t>411705</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>8611</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12719</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>162518</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154758</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165834</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>185287</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>180410</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>188150</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,16%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>176865</t>
+          <t>151753</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>164404</t>
+          <t>147593</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182503</t>
+          <t>154559</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>362152</t>
+          <t>314272</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>346605</t>
+          <t>306377</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>368695</t>
+          <t>318949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4743</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1809</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10120</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6813</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2907</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7278</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4912</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1847</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9841</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>164633</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>159256</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>167567</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>165060</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>161149</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167199</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>164238</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>159867</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>166393</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,55%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>176326</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>171397</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>179391</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,57%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>468</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>341387</t>
+          <t>328871</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>335079</t>
+          <t>323111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>345567</t>
+          <t>332543</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23574</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16067</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33293</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>14095</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8724</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>21433</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41195</t>
+          <t>23575</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41255</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30855</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58133</t>
+          <t>50180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>677255</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>667536</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>684762</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>923</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>651245</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>643907</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>656616</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>734812</t>
+          <t>614241</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>720777</t>
+          <t>605258</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>743244</t>
+          <t>619571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1386057</t>
+          <t>1291496</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1369179</t>
+          <t>1279482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1396457</t>
+          <t>1301282</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
